--- a/Figuras/CR-3112_28-09-24_AGGREGATED/CR-3112_28-09-24_AGGREGATED_sensibilidade.xlsx
+++ b/Figuras/CR-3112_28-09-24_AGGREGATED/CR-3112_28-09-24_AGGREGATED_sensibilidade.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,11 +546,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Preco Diesel</t>
+          <t>Caso base</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.69</v>
+        <v>5.78</v>
       </c>
       <c r="D2" t="n">
         <v>5.3</v>
@@ -586,31 +586,31 @@
         <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1335.04</v>
+        <v>1401.344</v>
       </c>
       <c r="S2" t="n">
-        <v>286.72</v>
+        <v>229.376</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.6208</v>
       </c>
       <c r="U2" t="n">
-        <v>286.72</v>
+        <v>231.9968</v>
       </c>
       <c r="V2" t="n">
-        <v>1425</v>
+        <v>1600</v>
       </c>
       <c r="W2" t="n">
-        <v>8450773.837511903</v>
+        <v>12217613.5070698</v>
       </c>
     </row>
     <row r="3">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.46</v>
+        <v>3.69</v>
       </c>
       <c r="D3" t="n">
         <v>5.3</v>
@@ -680,10 +680,10 @@
         <v>286.72</v>
       </c>
       <c r="V3" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="W3" t="n">
-        <v>17942054.37383052</v>
+        <v>8450773.837511903</v>
       </c>
     </row>
     <row r="4">
@@ -692,32 +692,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cotacao Dolar</t>
+          <t>Preco Diesel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.78</v>
+        <v>7.46</v>
       </c>
       <c r="D4" t="n">
-        <v>4.58</v>
+        <v>5.3</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>45.8</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>12.8</v>
       </c>
       <c r="H4" t="n">
-        <v>58.624</v>
+        <v>67.84</v>
       </c>
       <c r="I4" t="n">
         <v>9.75</v>
       </c>
       <c r="J4" t="n">
-        <v>44.655</v>
+        <v>51.675</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -753,10 +753,10 @@
         <v>286.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="W4" t="n">
-        <v>13826509.19235652</v>
+        <v>17942054.37383052</v>
       </c>
     </row>
     <row r="5">
@@ -772,25 +772,25 @@
         <v>5.78</v>
       </c>
       <c r="D5" t="n">
-        <v>6.31</v>
+        <v>4.58</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>63.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="G5" t="n">
         <v>12.8</v>
       </c>
       <c r="H5" t="n">
-        <v>80.768</v>
+        <v>58.624</v>
       </c>
       <c r="I5" t="n">
         <v>9.75</v>
       </c>
       <c r="J5" t="n">
-        <v>61.52249999999999</v>
+        <v>44.655</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -808,7 +808,7 @@
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -826,10 +826,10 @@
         <v>286.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1475</v>
+        <v>1275</v>
       </c>
       <c r="W5" t="n">
-        <v>13552614.21642635</v>
+        <v>13826509.19235652</v>
       </c>
     </row>
     <row r="6">
@@ -838,32 +838,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Preco Razao Elepot</t>
+          <t>Cotacao Dolar</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5.78</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3</v>
+        <v>6.31</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>63.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>12.8</v>
       </c>
       <c r="H6" t="n">
-        <v>67.84</v>
+        <v>80.768</v>
       </c>
       <c r="I6" t="n">
         <v>9.75</v>
       </c>
       <c r="J6" t="n">
-        <v>51.675</v>
+        <v>61.52249999999999</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -878,31 +878,31 @@
         <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1401.344</v>
+        <v>1335.04</v>
       </c>
       <c r="S6" t="n">
-        <v>229.376</v>
+        <v>286.72</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6208</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>231.9968</v>
+        <v>286.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="W6" t="n">
-        <v>12270613.5070698</v>
+        <v>13552614.21642635</v>
       </c>
     </row>
     <row r="7">
@@ -921,10 +921,10 @@
         <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>26.5</v>
       </c>
       <c r="G7" t="n">
         <v>12.8</v>
@@ -975,7 +975,7 @@
         <v>1600</v>
       </c>
       <c r="W7" t="n">
-        <v>12111613.5070698</v>
+        <v>12270613.5070698</v>
       </c>
     </row>
     <row r="8">
@@ -984,7 +984,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Preco Bat</t>
+          <t>Preco Razao Elepot</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -994,16 +994,16 @@
         <v>5.3</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="H8" t="n">
-        <v>33.92</v>
+        <v>67.84</v>
       </c>
       <c r="I8" t="n">
         <v>9.75</v>
@@ -1048,7 +1048,7 @@
         <v>1600</v>
       </c>
       <c r="W8" t="n">
-        <v>12514035.1662118</v>
+        <v>12111613.5070698</v>
       </c>
     </row>
     <row r="9">
@@ -1073,10 +1073,10 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>34.688</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>183.8464</v>
+        <v>33.92</v>
       </c>
       <c r="I9" t="n">
         <v>9.75</v>
@@ -1100,10 +1100,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1401.344</v>
@@ -1121,7 +1121,7 @@
         <v>1600</v>
       </c>
       <c r="W9" t="n">
-        <v>11203851.43280414</v>
+        <v>12514035.1662118</v>
       </c>
     </row>
     <row r="10">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Preco UC</t>
+          <t>Preco Bat</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1146,16 +1146,16 @@
         <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>12.8</v>
+        <v>34.688</v>
       </c>
       <c r="H10" t="n">
-        <v>67.84</v>
+        <v>183.8464</v>
       </c>
       <c r="I10" t="n">
-        <v>5.85</v>
+        <v>9.75</v>
       </c>
       <c r="J10" t="n">
-        <v>31.005</v>
+        <v>51.675</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
@@ -1173,10 +1173,10 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1401.344</v>
@@ -1194,7 +1194,7 @@
         <v>1600</v>
       </c>
       <c r="W10" t="n">
-        <v>12231503.7470698</v>
+        <v>11203851.43280414</v>
       </c>
     </row>
     <row r="11">
@@ -1225,10 +1225,10 @@
         <v>67.84</v>
       </c>
       <c r="I11" t="n">
-        <v>13.65</v>
+        <v>5.85</v>
       </c>
       <c r="J11" t="n">
-        <v>72.345</v>
+        <v>31.005</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -1243,31 +1243,31 @@
         <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1335.04</v>
+        <v>1401.344</v>
       </c>
       <c r="S11" t="n">
-        <v>286.72</v>
+        <v>229.376</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.6208</v>
       </c>
       <c r="U11" t="n">
-        <v>286.72</v>
+        <v>231.9968</v>
       </c>
       <c r="V11" t="n">
-        <v>1475</v>
+        <v>1600</v>
       </c>
       <c r="W11" t="n">
-        <v>13712518.21971506</v>
+        <v>12231503.7470698</v>
       </c>
     </row>
     <row r="12">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C-rate</t>
+          <t>Preco UC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1298,13 +1298,13 @@
         <v>67.84</v>
       </c>
       <c r="I12" t="n">
-        <v>9.75</v>
+        <v>13.65</v>
       </c>
       <c r="J12" t="n">
-        <v>51.675</v>
+        <v>72.345</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -1313,34 +1313,34 @@
         <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1414.336</v>
+        <v>1335.04</v>
       </c>
       <c r="S12" t="n">
-        <v>276.48</v>
+        <v>286.72</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9984</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>277.4784</v>
+        <v>286.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="W12" t="n">
-        <v>6002769.071460526</v>
+        <v>13712518.21971506</v>
       </c>
     </row>
     <row r="13">
@@ -1377,7 +1377,7 @@
         <v>51.675</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>15</v>
@@ -1389,31 +1389,31 @@
         <v>27</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1029.888</v>
+        <v>1414.336</v>
       </c>
       <c r="S13" t="n">
-        <v>221.184</v>
+        <v>276.48</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.9984</v>
       </c>
       <c r="U13" t="n">
-        <v>221.184</v>
+        <v>277.4784</v>
       </c>
       <c r="V13" t="n">
-        <v>1175</v>
+        <v>1600</v>
       </c>
       <c r="W13" t="n">
-        <v>14192890.32849914</v>
+        <v>6002769.071460526</v>
       </c>
     </row>
     <row r="14">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nm_b min</t>
+          <t>C-rate</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1450,43 +1450,43 @@
         <v>51.675</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
         <v>11</v>
       </c>
       <c r="N14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1401.344</v>
+        <v>1029.888</v>
       </c>
       <c r="S14" t="n">
-        <v>229.376</v>
+        <v>221.184</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6208</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>231.9968</v>
+        <v>221.184</v>
       </c>
       <c r="V14" t="n">
-        <v>1600</v>
+        <v>1175</v>
       </c>
       <c r="W14" t="n">
-        <v>12217613.5070698</v>
+        <v>14192890.32849914</v>
       </c>
     </row>
     <row r="15">
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nm_uc min</t>
+          <t>Nm_b min</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1599,10 +1599,10 @@
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N16" t="n">
         <v>28</v>
@@ -1675,7 +1675,7 @@
         <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
         <v>28</v>
@@ -1705,6 +1705,79 @@
         <v>1600</v>
       </c>
       <c r="W17" t="n">
+        <v>12217613.5070698</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1401.344</v>
+      </c>
+      <c r="S18" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.6208</v>
+      </c>
+      <c r="U18" t="n">
+        <v>231.9968</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1600</v>
+      </c>
+      <c r="W18" t="n">
         <v>12217613.5070698</v>
       </c>
     </row>
